--- a/test-output/CreatedUsers.xlsx
+++ b/test-output/CreatedUsers.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="122">
   <si>
     <t>First Name</t>
   </si>
@@ -284,6 +284,108 @@
   </si>
   <si>
     <t>SeleniumUser.4c504@infor.com</t>
+  </si>
+  <si>
+    <t>d6614</t>
+  </si>
+  <si>
+    <t>SeleniumUser.d6614@infor.com</t>
+  </si>
+  <si>
+    <t>67643</t>
+  </si>
+  <si>
+    <t>SeleniumUser.67643@infor.com</t>
+  </si>
+  <si>
+    <t>93f81</t>
+  </si>
+  <si>
+    <t>SeleniumUser.93f81@infor.com</t>
+  </si>
+  <si>
+    <t>dddc7</t>
+  </si>
+  <si>
+    <t>SeleniumUser.dddc7@infor.com</t>
+  </si>
+  <si>
+    <t>fcf14</t>
+  </si>
+  <si>
+    <t>SeleniumUser.fcf14@infor.com</t>
+  </si>
+  <si>
+    <t>7179e</t>
+  </si>
+  <si>
+    <t>SeleniumUser.7179e@infor.com</t>
+  </si>
+  <si>
+    <t>20afc</t>
+  </si>
+  <si>
+    <t>SeleniumUser.20afc@infor.com</t>
+  </si>
+  <si>
+    <t>9681f</t>
+  </si>
+  <si>
+    <t>SeleniumUser.9681f@infor.com</t>
+  </si>
+  <si>
+    <t>2450f</t>
+  </si>
+  <si>
+    <t>SeleniumUser.2450f@infor.com</t>
+  </si>
+  <si>
+    <t>9f589</t>
+  </si>
+  <si>
+    <t>SeleniumUser.9f589@infor.com</t>
+  </si>
+  <si>
+    <t>9b357</t>
+  </si>
+  <si>
+    <t>SeleniumUser.9b357@infor.com</t>
+  </si>
+  <si>
+    <t>b4e60</t>
+  </si>
+  <si>
+    <t>SeleniumUser.b4e60@infor.com</t>
+  </si>
+  <si>
+    <t>c7958</t>
+  </si>
+  <si>
+    <t>SeleniumUser.c7958@infor.com</t>
+  </si>
+  <si>
+    <t>dd58f</t>
+  </si>
+  <si>
+    <t>SeleniumUser.dd58f@infor.com</t>
+  </si>
+  <si>
+    <t>bf486</t>
+  </si>
+  <si>
+    <t>SeleniumUser.bf486@infor.com</t>
+  </si>
+  <si>
+    <t>42f71</t>
+  </si>
+  <si>
+    <t>SeleniumUser.42f71@infor.com</t>
+  </si>
+  <si>
+    <t>d8d24</t>
+  </si>
+  <si>
+    <t>SeleniumUser.d8d24@infor.com</t>
   </si>
 </sst>
 </file>
@@ -666,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="12.4453125"/>
@@ -1147,6 +1249,193 @@
         <v>87</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test-output/CreatedUsers.xlsx
+++ b/test-output/CreatedUsers.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="160">
   <si>
     <t>First Name</t>
   </si>
@@ -386,6 +386,120 @@
   </si>
   <si>
     <t>SeleniumUser.d8d24@infor.com</t>
+  </si>
+  <si>
+    <t>d2611</t>
+  </si>
+  <si>
+    <t>SeleniumUser.d2611@infor.com</t>
+  </si>
+  <si>
+    <t>3b098</t>
+  </si>
+  <si>
+    <t>SeleniumUser.3b098@infor.com</t>
+  </si>
+  <si>
+    <t>c20c7</t>
+  </si>
+  <si>
+    <t>SeleniumUser.c20c7@infor.com</t>
+  </si>
+  <si>
+    <t>a41be</t>
+  </si>
+  <si>
+    <t>SeleniumUser.a41be@infor.com</t>
+  </si>
+  <si>
+    <t>d6c3d</t>
+  </si>
+  <si>
+    <t>SeleniumUser.d6c3d@infor.com</t>
+  </si>
+  <si>
+    <t>ae325</t>
+  </si>
+  <si>
+    <t>SeleniumUser.ae325@infor.com</t>
+  </si>
+  <si>
+    <t>aa549</t>
+  </si>
+  <si>
+    <t>SeleniumUser.aa549@infor.com</t>
+  </si>
+  <si>
+    <t>ae758</t>
+  </si>
+  <si>
+    <t>SeleniumUser.ae758@infor.com</t>
+  </si>
+  <si>
+    <t>a936d</t>
+  </si>
+  <si>
+    <t>SeleniumUser.a936d@infor.com</t>
+  </si>
+  <si>
+    <t>a05a8</t>
+  </si>
+  <si>
+    <t>SeleniumUser.a05a8@infor.com</t>
+  </si>
+  <si>
+    <t>6bea0</t>
+  </si>
+  <si>
+    <t>SeleniumUser.6bea0@infor.com</t>
+  </si>
+  <si>
+    <t>a35e1</t>
+  </si>
+  <si>
+    <t>SeleniumUser.a35e1@infor.com</t>
+  </si>
+  <si>
+    <t>6ef80</t>
+  </si>
+  <si>
+    <t>SeleniumUser.6ef80@infor.com</t>
+  </si>
+  <si>
+    <t>d7c29</t>
+  </si>
+  <si>
+    <t>SeleniumUser.d7c29@infor.com</t>
+  </si>
+  <si>
+    <t>766e2</t>
+  </si>
+  <si>
+    <t>SeleniumUser.766e2@infor.com</t>
+  </si>
+  <si>
+    <t>b66cc</t>
+  </si>
+  <si>
+    <t>SeleniumUser.b66cc@infor.com</t>
+  </si>
+  <si>
+    <t>30972</t>
+  </si>
+  <si>
+    <t>SeleniumUser.30972@infor.com</t>
+  </si>
+  <si>
+    <t>e58f8</t>
+  </si>
+  <si>
+    <t>SeleniumUser.e58f8@infor.com</t>
+  </si>
+  <si>
+    <t>f4abd</t>
+  </si>
+  <si>
+    <t>SeleniumUser.f4abd@infor.com</t>
   </si>
 </sst>
 </file>
@@ -768,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="12.4453125"/>
@@ -1436,6 +1550,215 @@
         <v>121</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
